--- a/artfynd/A 59462-2023 artfynd.xlsx
+++ b/artfynd/A 59462-2023 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125015236</v>
+        <v>125015228</v>
       </c>
       <c r="B3" t="n">
-        <v>96985</v>
+        <v>98018</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -821,12 +821,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575985</v>
+        <v>575762</v>
       </c>
       <c r="R3" t="n">
-        <v>6689286</v>
+        <v>6689450</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,19 +868,9 @@
           <t>2024-11-06</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,6 +879,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -900,7 +891,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Andreas Svensson</t>
+          <t>Albin Kozma</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -911,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125015228</v>
+        <v>125015260</v>
       </c>
       <c r="B4" t="n">
-        <v>98018</v>
+        <v>96985</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,48 +918,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>221941</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>NV om Horndal, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575762</v>
+        <v>575985</v>
       </c>
       <c r="R4" t="n">
-        <v>6689450</v>
+        <v>6689286</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,12 +972,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,7 +986,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1021,7 +997,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Albin Kozma</t>
+          <t>Britta Lidberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 59462-2023 artfynd.xlsx
+++ b/artfynd/A 59462-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125015261</v>
+        <v>125015485</v>
       </c>
       <c r="B2" t="n">
-        <v>96982</v>
+        <v>91012</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221946</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>NV om Horndal, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576010</v>
+        <v>576040</v>
       </c>
       <c r="R2" t="n">
-        <v>6689261</v>
+        <v>6689188</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,12 +756,18 @@
           <t>2024-05-07</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Tog kollekt</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -902,10 +911,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125015260</v>
+        <v>125015261</v>
       </c>
       <c r="B4" t="n">
-        <v>96985</v>
+        <v>96982</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -918,16 +927,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221941</v>
+        <v>221946</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -942,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575985</v>
+        <v>576010</v>
       </c>
       <c r="R4" t="n">
-        <v>6689286</v>
+        <v>6689261</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125015485</v>
+        <v>125015260</v>
       </c>
       <c r="B5" t="n">
-        <v>91012</v>
+        <v>96985</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,41 +1029,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>221941</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>NV om Horndal, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576040</v>
+        <v>575985</v>
       </c>
       <c r="R5" t="n">
-        <v>6689188</v>
+        <v>6689286</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1089,18 +1095,12 @@
           <t>2024-05-07</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Tog kollekt</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 59462-2023 artfynd.xlsx
+++ b/artfynd/A 59462-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125015485</v>
+        <v>125015260</v>
       </c>
       <c r="B2" t="n">
-        <v>91012</v>
+        <v>96985</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>221941</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>NV om Horndal, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576040</v>
+        <v>575985</v>
       </c>
       <c r="R2" t="n">
-        <v>6689188</v>
+        <v>6689286</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,18 +753,12 @@
           <t>2024-05-07</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Tog kollekt</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -911,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125015261</v>
+        <v>125015485</v>
       </c>
       <c r="B4" t="n">
-        <v>96982</v>
+        <v>91012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,38 +914,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221946</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>NV om Horndal, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576010</v>
+        <v>576040</v>
       </c>
       <c r="R4" t="n">
-        <v>6689261</v>
+        <v>6689188</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,12 +983,18 @@
           <t>2024-05-07</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Tog kollekt</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1017,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125015260</v>
+        <v>125015261</v>
       </c>
       <c r="B5" t="n">
-        <v>96985</v>
+        <v>96982</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,16 +1033,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221941</v>
+        <v>221946</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575985</v>
+        <v>576010</v>
       </c>
       <c r="R5" t="n">
-        <v>6689286</v>
+        <v>6689261</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 59462-2023 artfynd.xlsx
+++ b/artfynd/A 59462-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125015260</v>
+        <v>125015236</v>
       </c>
       <c r="B2" t="n">
         <v>96985</v>
@@ -708,7 +708,21 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>NV om Horndal, Dlr</t>
@@ -745,12 +759,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,7 +794,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Britta Lidberg</t>
+          <t>Andreas Svensson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">

--- a/artfynd/A 59462-2023 artfynd.xlsx
+++ b/artfynd/A 59462-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125015236</v>
+        <v>125015261</v>
       </c>
       <c r="B2" t="n">
-        <v>96985</v>
+        <v>96982</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221941</v>
+        <v>221946</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,31 +708,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>NV om Horndal, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575985</v>
+        <v>576010</v>
       </c>
       <c r="R2" t="n">
-        <v>6689286</v>
+        <v>6689261</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,22 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:20</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:20</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Andreas Svensson</t>
+          <t>Britta Lidberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -805,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125015228</v>
+        <v>125015485</v>
       </c>
       <c r="B3" t="n">
-        <v>98018</v>
+        <v>91012</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,52 +793,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>NV om Horndal, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575762</v>
+        <v>576040</v>
       </c>
       <c r="R3" t="n">
-        <v>6689450</v>
+        <v>6689188</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,12 +854,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-05-07</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Tog kollekt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,7 +885,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Albin Kozma</t>
+          <t>Britta Lidberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -926,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125015485</v>
+        <v>125015228</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
+        <v>98018</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -938,41 +908,52 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>NV om Horndal, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576040</v>
+        <v>575762</v>
       </c>
       <c r="R4" t="n">
-        <v>6689188</v>
+        <v>6689450</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,17 +980,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Tog kollekt</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,7 +1006,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Britta Lidberg</t>
+          <t>Albin Kozma</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1041,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125015261</v>
+        <v>125015236</v>
       </c>
       <c r="B5" t="n">
-        <v>96982</v>
+        <v>96985</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1057,16 +1033,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221946</v>
+        <v>221941</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1074,17 +1050,31 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>NV om Horndal, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576010</v>
+        <v>575985</v>
       </c>
       <c r="R5" t="n">
-        <v>6689261</v>
+        <v>6689286</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,12 +1101,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Britta Lidberg</t>
+          <t>Andreas Svensson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">

--- a/artfynd/A 59462-2023 artfynd.xlsx
+++ b/artfynd/A 59462-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125015261</v>
+        <v>125015236</v>
       </c>
       <c r="B2" t="n">
-        <v>96982</v>
+        <v>96985</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221946</v>
+        <v>221941</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,17 +708,31 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>NV om Horndal, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576010</v>
+        <v>575985</v>
       </c>
       <c r="R2" t="n">
-        <v>6689261</v>
+        <v>6689286</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +759,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,7 +794,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Britta Lidberg</t>
+          <t>Andreas Svensson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -896,10 +920,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125015228</v>
+        <v>125015261</v>
       </c>
       <c r="B4" t="n">
-        <v>98018</v>
+        <v>96982</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,48 +936,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>221946</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>NV om Horndal, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575762</v>
+        <v>576010</v>
       </c>
       <c r="R4" t="n">
-        <v>6689450</v>
+        <v>6689261</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,12 +990,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,7 +1004,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1006,7 +1015,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Albin Kozma</t>
+          <t>Britta Lidberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1017,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125015236</v>
+        <v>125015228</v>
       </c>
       <c r="B5" t="n">
-        <v>96985</v>
+        <v>98018</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,21 +1042,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221941</v>
+        <v>219790</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1057,12 +1066,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1071,10 +1080,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575985</v>
+        <v>575762</v>
       </c>
       <c r="R5" t="n">
-        <v>6689286</v>
+        <v>6689450</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1104,19 +1113,9 @@
           <t>2024-11-06</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>12:20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,6 +1124,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Andreas Svensson</t>
+          <t>Albin Kozma</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">

--- a/artfynd/A 59462-2023 artfynd.xlsx
+++ b/artfynd/A 59462-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125015236</v>
+        <v>125015260</v>
       </c>
       <c r="B2" t="n">
         <v>96985</v>
@@ -708,21 +708,7 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>NV om Horndal, Dlr</t>
@@ -759,22 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:20</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:20</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Andreas Svensson</t>
+          <t>Britta Lidberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">

--- a/artfynd/A 59462-2023 artfynd.xlsx
+++ b/artfynd/A 59462-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125015260</v>
+        <v>125015236</v>
       </c>
       <c r="B2" t="n">
         <v>96985</v>
@@ -708,7 +708,21 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>NV om Horndal, Dlr</t>
@@ -745,12 +759,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,7 +794,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Britta Lidberg</t>
+          <t>Andreas Svensson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -781,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125015485</v>
+        <v>125015228</v>
       </c>
       <c r="B3" t="n">
-        <v>91012</v>
+        <v>98018</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,41 +817,52 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>NV om Horndal, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576040</v>
+        <v>575762</v>
       </c>
       <c r="R3" t="n">
-        <v>6689188</v>
+        <v>6689450</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -854,17 +889,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Tog kollekt</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,7 +915,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Britta Lidberg</t>
+          <t>Albin Kozma</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -1002,10 +1032,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125015228</v>
+        <v>125015485</v>
       </c>
       <c r="B5" t="n">
-        <v>98018</v>
+        <v>91012</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,52 +1044,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>NV om Horndal, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575762</v>
+        <v>576040</v>
       </c>
       <c r="R5" t="n">
-        <v>6689450</v>
+        <v>6689188</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,12 +1105,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-05-07</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Tog kollekt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,7 +1136,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Albin Kozma</t>
+          <t>Britta Lidberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">

--- a/artfynd/A 59462-2023 artfynd.xlsx
+++ b/artfynd/A 59462-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125015236</v>
+        <v>125015485</v>
       </c>
       <c r="B2" t="n">
-        <v>96985</v>
+        <v>91012</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,52 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221941</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>NV om Horndal, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575985</v>
+        <v>576040</v>
       </c>
       <c r="R2" t="n">
-        <v>6689286</v>
+        <v>6689188</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,22 +748,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:20</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:20</t>
+          <t>2024-05-07</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Tog kollekt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,6 +767,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -794,7 +779,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Andreas Svensson</t>
+          <t>Britta Lidberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -805,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125015228</v>
+        <v>125015236</v>
       </c>
       <c r="B3" t="n">
-        <v>98018</v>
+        <v>96985</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,21 +806,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>221941</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -845,12 +830,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -859,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575762</v>
+        <v>575985</v>
       </c>
       <c r="R3" t="n">
-        <v>6689450</v>
+        <v>6689286</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,9 +877,19 @@
           <t>2024-11-06</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,7 +898,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -915,7 +909,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Albin Kozma</t>
+          <t>Andreas Svensson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -926,10 +920,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125015261</v>
+        <v>125015228</v>
       </c>
       <c r="B4" t="n">
-        <v>96982</v>
+        <v>98018</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -942,34 +936,48 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221946</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>NV om Horndal, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576010</v>
+        <v>575762</v>
       </c>
       <c r="R4" t="n">
-        <v>6689261</v>
+        <v>6689450</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,12 +1004,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,6 +1018,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1021,7 +1030,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Britta Lidberg</t>
+          <t>Albin Kozma</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1032,10 +1041,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125015485</v>
+        <v>125015261</v>
       </c>
       <c r="B5" t="n">
-        <v>91012</v>
+        <v>96982</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1044,41 +1053,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>221946</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>NV om Horndal, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576040</v>
+        <v>576010</v>
       </c>
       <c r="R5" t="n">
-        <v>6689188</v>
+        <v>6689261</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1113,18 +1119,12 @@
           <t>2024-05-07</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Tog kollekt</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 59462-2023 artfynd.xlsx
+++ b/artfynd/A 59462-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125015485</v>
+        <v>125015260</v>
       </c>
       <c r="B2" t="n">
-        <v>91012</v>
+        <v>97153</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>221941</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>NV om Horndal, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576040</v>
+        <v>575985</v>
       </c>
       <c r="R2" t="n">
-        <v>6689188</v>
+        <v>6689286</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,18 +753,12 @@
           <t>2024-05-07</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Tog kollekt</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -790,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125015236</v>
+        <v>125015261</v>
       </c>
       <c r="B3" t="n">
-        <v>96985</v>
+        <v>97150</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,16 +797,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>221946</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -823,31 +814,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>NV om Horndal, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575985</v>
+        <v>576010</v>
       </c>
       <c r="R3" t="n">
-        <v>6689286</v>
+        <v>6689261</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,22 +851,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:20</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:20</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Andreas Svensson</t>
+          <t>Britta Lidberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -923,7 +890,7 @@
         <v>125015228</v>
       </c>
       <c r="B4" t="n">
-        <v>98018</v>
+        <v>98186</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1041,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125015261</v>
+        <v>125015485</v>
       </c>
       <c r="B5" t="n">
-        <v>96982</v>
+        <v>91166</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1053,38 +1020,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221946</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>NV om Horndal, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576010</v>
+        <v>576040</v>
       </c>
       <c r="R5" t="n">
-        <v>6689261</v>
+        <v>6689188</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,12 +1089,18 @@
           <t>2024-05-07</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Tog kollekt</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 59462-2023 artfynd.xlsx
+++ b/artfynd/A 59462-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125015260</v>
+        <v>125015236</v>
       </c>
       <c r="B2" t="n">
         <v>97153</v>
@@ -708,7 +708,21 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>NV om Horndal, Dlr</t>
@@ -745,12 +759,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,7 +794,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Britta Lidberg</t>
+          <t>Andreas Svensson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -781,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125015261</v>
+        <v>125015485</v>
       </c>
       <c r="B3" t="n">
-        <v>97150</v>
+        <v>91166</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,38 +817,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221946</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>NV om Horndal, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576010</v>
+        <v>576040</v>
       </c>
       <c r="R3" t="n">
-        <v>6689261</v>
+        <v>6689188</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -859,12 +886,18 @@
           <t>2024-05-07</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Tog kollekt</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -887,10 +920,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125015228</v>
+        <v>125015261</v>
       </c>
       <c r="B4" t="n">
-        <v>98186</v>
+        <v>97150</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,48 +936,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>221946</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>NV om Horndal, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575762</v>
+        <v>576010</v>
       </c>
       <c r="R4" t="n">
-        <v>6689450</v>
+        <v>6689261</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,12 +990,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -985,7 +1004,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -997,7 +1015,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Albin Kozma</t>
+          <t>Britta Lidberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1008,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125015485</v>
+        <v>125015228</v>
       </c>
       <c r="B5" t="n">
-        <v>91166</v>
+        <v>98186</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,41 +1038,52 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>219790</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>NV om Horndal, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576040</v>
+        <v>575762</v>
       </c>
       <c r="R5" t="n">
-        <v>6689188</v>
+        <v>6689450</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,17 +1110,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Tog kollekt</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,7 +1136,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Britta Lidberg</t>
+          <t>Albin Kozma</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">

--- a/artfynd/A 59462-2023 artfynd.xlsx
+++ b/artfynd/A 59462-2023 artfynd.xlsx
@@ -675,64 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125015236</v>
+        <v>125015485</v>
       </c>
       <c r="B2" t="n">
-        <v>97153</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91166</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221941</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>NV om Horndal, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575985</v>
+        <v>576040</v>
       </c>
       <c r="R2" t="n">
-        <v>6689286</v>
+        <v>6689188</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,22 +743,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:20</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:20</t>
+          <t>2024-05-07</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Tog kollekt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,6 +762,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -794,7 +774,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Andreas Svensson</t>
+          <t>Britta Lidberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -805,53 +785,59 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125015485</v>
+        <v>125015236</v>
       </c>
       <c r="B3" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97153</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>221941</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>NV om Horndal, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576040</v>
+        <v>575985</v>
       </c>
       <c r="R3" t="n">
-        <v>6689188</v>
+        <v>6689286</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -878,17 +864,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Tog kollekt</t>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,7 +888,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -909,7 +899,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Britta Lidberg</t>
+          <t>Andreas Svensson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -925,11 +915,6 @@
       <c r="B4" t="n">
         <v>97150</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>LC</t>
@@ -1030,11 +1015,6 @@
       </c>
       <c r="B5" t="n">
         <v>98186</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 59462-2023 artfynd.xlsx
+++ b/artfynd/A 59462-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125015485</v>
       </c>
       <c r="B2" t="n">
-        <v>91166</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -769,7 +769,7 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Andreas Svensson</t>
+          <t>Andreas Ekedahl</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125015236</v>
+        <v>125015228</v>
       </c>
       <c r="B3" t="n">
-        <v>97153</v>
+        <v>99035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -796,21 +796,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -820,12 +820,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575985</v>
+        <v>575762</v>
       </c>
       <c r="R3" t="n">
-        <v>6689286</v>
+        <v>6689450</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,19 +867,9 @@
           <t>2024-11-06</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,18 +878,19 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Andreas Svensson</t>
+          <t>Andreas Ekedahl</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Andreas Svensson</t>
+          <t>Albin Kozma</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -910,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125015261</v>
+        <v>125015236</v>
       </c>
       <c r="B4" t="n">
-        <v>97150</v>
+        <v>97989</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -921,16 +912,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221946</v>
+        <v>221941</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -938,17 +929,31 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>NV om Horndal, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576010</v>
+        <v>575985</v>
       </c>
       <c r="R4" t="n">
-        <v>6689261</v>
+        <v>6689286</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -975,12 +980,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -995,12 +1010,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Andreas Svensson</t>
+          <t>Andreas Ekedahl</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Britta Lidberg</t>
+          <t>Andreas Ekedahl</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1011,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125015228</v>
+        <v>125015261</v>
       </c>
       <c r="B5" t="n">
-        <v>98186</v>
+        <v>97986</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,48 +1037,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>221946</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>NV om Horndal, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575762</v>
+        <v>576010</v>
       </c>
       <c r="R5" t="n">
-        <v>6689450</v>
+        <v>6689261</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1090,12 +1091,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1104,19 +1105,18 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Andreas Svensson</t>
+          <t>Andreas Ekedahl</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Albin Kozma</t>
+          <t>Britta Lidberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">

--- a/artfynd/A 59462-2023 artfynd.xlsx
+++ b/artfynd/A 59462-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -782,6 +787,11 @@
           <t>NVI Horndal 2024</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125015485</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -898,6 +908,11 @@
           <t>NVI Horndal 2024</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125015228</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1023,6 +1038,11 @@
           <t>NVI Horndal 2024</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125015236</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1124,8 +1144,19 @@
           <t>NVI Horndal 2024</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125015261</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>